--- a/stories/arbres/ATOM-VIV.ANI.002-08.xlsx
+++ b/stories/arbres/ATOM-VIV.ANI.002-08.xlsx
@@ -481,7 +481,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B29"/>
+  <dimension ref="A1:B30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -602,7 +602,6 @@
           <t>secondary_lessons</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -819,6 +818,18 @@
       <c r="B29" t="inlineStr">
         <is>
           <t>xlsx-arbre-v1</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>voice_cast</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>voix-roles-v1</t>
         </is>
       </c>
     </row>
@@ -833,7 +844,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AV6"/>
+  <dimension ref="A1:AW6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -1127,6 +1138,11 @@
           <t>notes</t>
         </is>
       </c>
+      <c r="AW1" t="inlineStr">
+        <is>
+          <t>script</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -1151,7 +1167,7 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Eva est à l'écurie avec maman. Papa ouvre la porte. Dans la paille, un chat miaule. Une chatte se lèche. Un chaton suit la chatte. Maman dit : chat, chatte, chaton. Ce sont trois noms. Dans le pré, un cheval mange. Une jument est là. Un poulain reste près. Papa dit : cheval, jument, poulain. Près du foin, un coq chante. Une poule picore. Un poussin suit. Maman dit : coq, poule, poussin. Eva répète les trois noms de la famille. Elle caresse la paille. Ça sent le foin.</t>
+          <t>Eva est à l'écurie avec maman. Papa ouvre la porte. Dans la paille, un chat miaule. Une chatte se lèche. Un chaton suit la chatte. Chat, chatte, chaton. Ce sont trois noms. Dans le pré, un cheval mange. Une jument est là. Un poulain reste près. Cheval, jument, poulain. Près du foin, un coq chante. Une poule picore. Un poussin suit. Coq, poule, poussin. Eva répète les trois noms de la famille. Elle caresse la paille. Ça sent le foin.</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
@@ -1289,6 +1305,17 @@
         <v>8</v>
       </c>
       <c r="AV2" s="2" t="inlineStr"/>
+      <c r="AW2" t="inlineStr">
+        <is>
+          <t>narrateur|Eva est à l'écurie avec maman. Papa ouvre la porte. Dans la paille, un chat miaule. Une chatte se lèche. Un chaton suit la chatte.
+maman|Chat, chatte, chaton. Ce sont trois noms.
+narrateur|Dans le pré, un cheval mange. Une jument est là. Un poulain reste près.
+papa|Cheval, jument, poulain. Près du foin, un coq chante.
+narrateur|Une poule picore. Un poussin suit.
+maman|Coq, poule, poussin.
+narrateur|Eva répète les trois noms de la famille. Elle caresse la paille. Ça sent le foin.</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1465,6 +1492,11 @@
       <c r="AV3" s="2" t="inlineStr">
         <is>
           <t>question d'écoute, ne change pas le cours</t>
+        </is>
+      </c>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>narrateur|Le chat, la chatte, et le petit. Quel est le petit ?</t>
         </is>
       </c>
     </row>
@@ -1633,6 +1665,11 @@
           <t>confirmation ; le moteur peut dire engine_ok/near avant ce chunk</t>
         </is>
       </c>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>narrateur|Eva a dit les trois noms. Chat, chatte, chaton. Cheval, jument, poulain.</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1791,6 +1828,11 @@
         <v>8</v>
       </c>
       <c r="AV5" s="2" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>narrateur|Eva sent le foin. Maman sourit. Ils rentrent.</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -1953,6 +1995,11 @@
         <v>8</v>
       </c>
       <c r="AV6" s="2" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV6"/>
@@ -1971,7 +2018,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A2"/>
+  <dimension ref="A1:A3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -1988,6 +2035,13 @@
       <c r="A2" t="inlineStr">
         <is>
           <t>conversion structurelle, prompts de choix alignés, TTS profilé</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>F-AUD-006 scripts multi-voix, sans « X dit »</t>
         </is>
       </c>
     </row>

--- a/stories/arbres/ATOM-VIV.ANI.002-08.xlsx
+++ b/stories/arbres/ATOM-VIV.ANI.002-08.xlsx
@@ -844,7 +844,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AW6"/>
+  <dimension ref="A1:AX6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -1143,6 +1143,11 @@
           <t>script</t>
         </is>
       </c>
+      <c r="AX1" t="inlineStr">
+        <is>
+          <t>sons</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -1316,6 +1321,7 @@
 narrateur|Eva répète les trois noms de la famille. Elle caresse la paille. Ça sent le foin.</t>
         </is>
       </c>
+      <c r="AX2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1499,6 +1505,7 @@
           <t>narrateur|Le chat, la chatte, et le petit. Quel est le petit ?</t>
         </is>
       </c>
+      <c r="AX3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -1670,6 +1677,7 @@
           <t>narrateur|Eva a dit les trois noms. Chat, chatte, chaton. Cheval, jument, poulain.</t>
         </is>
       </c>
+      <c r="AX4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1833,6 +1841,7 @@
           <t>narrateur|Eva sent le foin. Maman sourit. Ils rentrent.</t>
         </is>
       </c>
+      <c r="AX5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -2000,6 +2009,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX6" t="inlineStr"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV6"/>
@@ -2018,7 +2028,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A3"/>
+  <dimension ref="A1:A5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -2042,6 +2052,20 @@
       <c r="A3" t="inlineStr">
         <is>
           <t>F-AUD-006 scripts multi-voix, sans « X dit »</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
         </is>
       </c>
     </row>
@@ -2056,7 +2080,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B15"/>
+  <dimension ref="A1:B16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -2243,6 +2267,18 @@
         </is>
       </c>
     </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>sons</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>ids de bruits (vide = silence). Le bruit se joue, puis l'histoire reprend au calme.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/stories/arbres/ATOM-VIV.ANI.002-08.xlsx
+++ b/stories/arbres/ATOM-VIV.ANI.002-08.xlsx
@@ -481,7 +481,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B30"/>
+  <dimension ref="A1:B31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -544,7 +544,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Eva dit les trois noms à l'écurie</t>
+          <t>La brosse du poney</t>
         </is>
       </c>
     </row>
@@ -830,6 +830,18 @@
       <c r="B30" t="inlineStr">
         <is>
           <t>voix-roles-v1</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>fil_rouge</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Aniss veut brosser le poney. La brosse tombe dans la paille. Il la ramasse près de papa et maman. Cheval, jument, poney. Ils restent ensemble.</t>
         </is>
       </c>
     </row>
@@ -1172,12 +1184,12 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Eva est à l'écurie avec maman. Papa ouvre la porte. Dans la paille, un chat miaule. Une chatte se lèche. Un chaton suit la chatte. Chat, chatte, chaton. Ce sont trois noms. Dans le pré, un cheval mange. Une jument est là. Un poulain reste près. Cheval, jument, poulain. Près du foin, un coq chante. Une poule picore. Un poussin suit. Coq, poule, poussin. Eva répète les trois noms de la famille. Elle caresse la paille. Ça sent le foin.</t>
+          <t>La porte de bois de l'écurie craque. L'air sent le cuir et le foin. Un rai de lumière coupe la paille. Aniss vit ici, avec papa et maman. Ses mains sont déjà un peu poudreuses. Je veux brosser le poney. Le poney du box du fond ? Oui. On y va ensemble. En ce moment, ils avancent entre les boxes. Un cheval noir souffle près de la porte. Le cheval ! Oui, Aniss. On passe près de lui, sans courir. Une jument alezane gratte la litière. La jument aussi. Tu les vois bien ? Oui. Le poney est au fond. Aniss fait un pas tout seul. On reste avec nous ? On brosse ensemble. Oui. Il revient entre papa et maman. Le poney pie attend, l'œil sombre. Le poney ! Cheval, jument, poney. Trois noms de la famille. Papa tend la brosse en crin. Aniss la prend. La brosse glisse, tombe dans la paille. Oh. On la cherche, tous les trois ? Aniss écarte la paille près des bottes. Le bois de la brosse reparaît. Je l'ai. Merci de rester avec nous. Tu brosses, on est là. Aniss pose la brosse sur l'encolure. Le poil du poney sent le foin chaud. Il est doux. Tout doux, comme ta main. Aniss brosse de l'encolure vers l'épaule. Le poney pie cligne, sans reculer. Il aime ça. Oui. On reste tous les trois. Le cheval noir gratte une fois, plus loin. La jument souffle dans sa litière. Ils écoutent. Toi aussi, tu écoutes. Un brin de paille colle à la brosse. On le retire ensemble ? Oui, papa. Maman pince le brin, Aniss tient le bois.</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Eva est à l'écurie avec maman. Papa ouvre la porte. Dans la paille, un chat miaule. Une chatte se lèche. Un chaton suit la chatte. Maman dit : chat, chatte, chaton. Ce sont &lt;emphasis level="moderate"&gt;trois&lt;/emphasis&gt; noms. Dans le pré, un cheval mange. Une jument est là. Un poulain reste près. Papa dit : cheval, jument, poulain. Près du foin, un coq chante. Une poule picore. Un poussin suit. Maman dit : coq, poule, poussin. Eva répète les trois noms de la famille. Elle caresse la paille. Ça sent le foin.&lt;/prosody&gt;&lt;break time="400ms"/&gt;&lt;/speak&gt;</t>
+          <t>La porte de bois de l'écurie craque. L'air sent le cuir et le foin. Un rai de lumière coupe la paille. Aniss vit ici, avec papa et maman. Ses mains sont déjà un peu poudreuses. Je veux brosser le poney. Le poney du box du fond ? Oui. On y va ensemble. En ce moment, ils avancent entre les boxes. Un cheval noir souffle près de la porte. Le cheval ! Oui, Aniss. On passe près de lui, sans courir. Une jument alezane gratte la litière. La jument aussi. Tu les vois bien ? Oui. Le poney est au fond. Aniss fait un pas tout seul. On reste avec nous ? On brosse ensemble. Oui. Il revient entre papa et maman. Le poney pie attend, l'œil sombre. Le poney ! Cheval, jument, poney. Trois noms de la famille. Papa tend la brosse en crin. Aniss la prend. La brosse glisse, tombe dans la paille. Oh. On la cherche, tous les trois ? Aniss écarte la paille près des bottes. Le bois de la brosse reparaît. Je l'ai. Merci de rester avec nous. Tu brosses, on est là. Aniss pose la brosse sur l'encolure. Le poil du poney sent le foin chaud. Il est doux. Tout doux, comme ta main. Aniss brosse de l'encolure vers l'épaule. Le poney pie cligne, sans reculer. Il aime ça. Oui. On reste tous les trois. Le cheval noir gratte une fois, plus loin. La jument souffle dans sa litière. Ils écoutent. Toi aussi, tu écoutes. Un brin de paille colle à la brosse. On le retire ensemble ? Oui, papa. Maman pince le brin, Aniss tient le bois.</t>
         </is>
       </c>
       <c r="G2" s="2" t="inlineStr">
@@ -1240,7 +1252,7 @@
         <v>0.92</v>
       </c>
       <c r="AB2" s="2" t="n">
-        <v>1.18</v>
+        <v>1.22</v>
       </c>
       <c r="AC2" s="2" t="inlineStr">
         <is>
@@ -1312,16 +1324,63 @@
       <c r="AV2" s="2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>narrateur|Eva est à l'écurie avec maman. Papa ouvre la porte. Dans la paille, un chat miaule. Une chatte se lèche. Un chaton suit la chatte.
-maman|Chat, chatte, chaton. Ce sont trois noms.
-narrateur|Dans le pré, un cheval mange. Une jument est là. Un poulain reste près.
-papa|Cheval, jument, poulain. Près du foin, un coq chante.
-narrateur|Une poule picore. Un poussin suit.
-maman|Coq, poule, poussin.
-narrateur|Eva répète les trois noms de la famille. Elle caresse la paille. Ça sent le foin.</t>
-        </is>
-      </c>
-      <c r="AX2" t="inlineStr"/>
+          <t>narrateur|La porte de bois de l'écurie craque.
+narrateur|L'air sent le cuir et le foin.
+narrateur|Un rai de lumière coupe la paille.
+narrateur|Aniss vit ici, avec papa et maman.
+narrateur|Ses mains sont déjà un peu poudreuses.
+enfant-m|Je veux brosser le poney.
+maman|Le poney du box du fond ?
+enfant-m|Oui.
+papa|On y va ensemble.
+narrateur|En ce moment, ils avancent entre les boxes.
+narrateur|Un cheval noir souffle près de la porte.
+enfant-m|Le cheval !
+papa|Oui, Aniss.
+papa|On passe près de lui, sans courir.
+narrateur|Une jument alezane gratte la litière.
+enfant-m|La jument aussi.
+maman|Tu les vois bien ?
+enfant-m|Oui.
+enfant-m|Le poney est au fond.
+narrateur|Aniss fait un pas tout seul.
+papa|On reste avec nous ?
+maman|On brosse ensemble.
+enfant-m|Oui.
+narrateur|Il revient entre papa et maman.
+narrateur|Le poney pie attend, l'œil sombre.
+enfant-m|Le poney !
+maman|Cheval, jument, poney.
+maman|Trois noms de la famille.
+narrateur|Papa tend la brosse en crin.
+narrateur|Aniss la prend.
+narrateur|La brosse glisse, tombe dans la paille.
+enfant-m|Oh.
+maman|On la cherche, tous les trois ?
+narrateur|Aniss écarte la paille près des bottes.
+narrateur|Le bois de la brosse reparaît.
+enfant-m|Je l'ai.
+papa|Merci de rester avec nous.
+papa|Tu brosses, on est là.
+narrateur|Aniss pose la brosse sur l'encolure.
+narrateur|Le poil du poney sent le foin chaud.
+enfant-m|Il est doux.
+maman|Tout doux, comme ta main.
+narrateur|Aniss brosse de l'encolure vers l'épaule.
+narrateur|Le poney pie cligne, sans reculer.
+enfant-m|Il aime ça.
+papa|Oui.
+papa|On reste tous les trois.
+narrateur|Le cheval noir gratte une fois, plus loin.
+narrateur|La jument souffle dans sa litière.
+enfant-m|Ils écoutent.
+maman|Toi aussi, tu écoutes.
+narrateur|Un brin de paille colle à la brosse.
+papa|On le retire ensemble ?
+enfant-m|Oui, papa.
+narrateur|Maman pince le brin, Aniss tient le bois.</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1346,12 +1405,12 @@
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
-          <t>Le chat, la chatte, et le petit. Quel est le petit ?</t>
+          <t>Aniss brosse qui, à l'écurie ?</t>
         </is>
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="medium"&gt;Le chat, la chatte, et le petit. Quel est le petit ?&lt;/prosody&gt;&lt;break time="250ms"/&gt;&lt;/speak&gt;</t>
+          <t>Aniss brosse qui, à l'écurie ?</t>
         </is>
       </c>
       <c r="G3" s="2" t="inlineStr">
@@ -1361,12 +1420,12 @@
       </c>
       <c r="H3" s="2" t="inlineStr">
         <is>
-          <t>chaton</t>
+          <t>poney</t>
         </is>
       </c>
       <c r="I3" s="2" t="inlineStr">
         <is>
-          <t>chaton | le chaton | petit | le petit</t>
+          <t>poney | le poney | un poney</t>
         </is>
       </c>
       <c r="J3" s="2" t="inlineStr">
@@ -1381,7 +1440,7 @@
       </c>
       <c r="L3" s="2" t="inlineStr">
         <is>
-          <t>Le petit du chat et de la chatte. Qui est-ce ?</t>
+          <t>C'est le poney. Qui Aniss brosse-t-il ?</t>
         </is>
       </c>
       <c r="M3" s="2" t="inlineStr"/>
@@ -1430,7 +1489,7 @@
         <v>0.86</v>
       </c>
       <c r="AB3" s="2" t="n">
-        <v>1.3</v>
+        <v>1.28</v>
       </c>
       <c r="AC3" s="2" t="inlineStr">
         <is>
@@ -1502,10 +1561,9 @@
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>narrateur|Le chat, la chatte, et le petit. Quel est le petit ?</t>
-        </is>
-      </c>
-      <c r="AX3" t="inlineStr"/>
+          <t>narrateur|Aniss brosse qui, à l'écurie ?</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -1530,12 +1588,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>Eva a dit les trois noms. Chat, chatte, chaton. Cheval, jument, poulain.</t>
+          <t>Le poney baisse un peu le cou. La poussière vole dans le rai de lumière. Ça le démangeait. Oui. C'est le poney du box. Tu restes avec nous ? Oui. On brosse ensemble. La brosse fait un bruit court, régulier. On reste encore un peu ? Oui, maman.</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Eva a dit les &lt;emphasis level="moderate"&gt;trois&lt;/emphasis&gt; noms. Chat, chatte, chaton. Cheval, jument, poulain.&lt;/prosody&gt;&lt;break time="450ms"/&gt;&lt;/speak&gt;</t>
+          <t>Le poney baisse un peu le cou. La poussière vole dans le rai de lumière. Ça le démangeait. Oui. C'est le poney du box. Tu restes avec nous ? Oui. On brosse ensemble. La brosse fait un bruit court, régulier. On reste encore un peu ? Oui, maman.</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -1598,7 +1656,7 @@
         <v>0.92</v>
       </c>
       <c r="AB4" s="2" t="n">
-        <v>1.18</v>
+        <v>1.22</v>
       </c>
       <c r="AC4" s="2" t="inlineStr">
         <is>
@@ -1674,10 +1732,19 @@
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>narrateur|Eva a dit les trois noms. Chat, chatte, chaton. Cheval, jument, poulain.</t>
-        </is>
-      </c>
-      <c r="AX4" t="inlineStr"/>
+          <t>narrateur|Le poney baisse un peu le cou.
+narrateur|La poussière vole dans le rai de lumière.
+enfant-m|Ça le démangeait.
+papa|Oui.
+papa|C'est le poney du box.
+maman|Tu restes avec nous ?
+enfant-m|Oui.
+enfant-m|On brosse ensemble.
+narrateur|La brosse fait un bruit court, régulier.
+maman|On reste encore un peu ?
+enfant-m|Oui, maman.</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1702,12 +1769,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>Eva sent le foin. Maman sourit. Ils rentrent.</t>
+          <t>Ils raccrochent la brosse au clou. Le cheval noir souffle encore. La jument gratte une dernière fois. Le poney est lisse. Tu as vu les trois ? Cheval, jument, poney. Et tu es resté avec nous. Aniss essuie ses mains dans la paille propre. Tes doigts sentent le poney. Et le foin. La porte de bois craque encore, un peu.</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Eva sent le foin. Maman sourit. Ils rentrent.&lt;/prosody&gt;&lt;break time="450ms"/&gt;&lt;/speak&gt;</t>
+          <t>Ils raccrochent la brosse au clou. Le cheval noir souffle encore. La jument gratte une dernière fois. Le poney est lisse. Tu as vu les trois ? Cheval, jument, poney. Et tu es resté avec nous. Aniss essuie ses mains dans la paille propre. Tes doigts sentent le poney. Et le foin. La porte de bois craque encore, un peu.</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -1770,7 +1837,7 @@
         <v>0.92</v>
       </c>
       <c r="AB5" s="2" t="n">
-        <v>1.18</v>
+        <v>1.22</v>
       </c>
       <c r="AC5" s="2" t="inlineStr">
         <is>
@@ -1838,10 +1905,19 @@
       <c r="AV5" s="2" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>narrateur|Eva sent le foin. Maman sourit. Ils rentrent.</t>
-        </is>
-      </c>
-      <c r="AX5" t="inlineStr"/>
+          <t>narrateur|Ils raccrochent la brosse au clou.
+narrateur|Le cheval noir souffle encore.
+narrateur|La jument gratte une dernière fois.
+enfant-m|Le poney est lisse.
+papa|Tu as vu les trois ?
+enfant-m|Cheval, jument, poney.
+maman|Et tu es resté avec nous.
+narrateur|Aniss essuie ses mains dans la paille propre.
+papa|Tes doigts sentent le poney.
+enfant-m|Et le foin.
+narrateur|La porte de bois craque encore, un peu.</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -1866,12 +1942,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>Il sent le foin. Sur tes mains aussi. Le poil du poney sent encore le foin.</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="low"&gt;L'histoire est finie.&lt;/prosody&gt;&lt;break time="600ms"/&gt;&lt;/speak&gt;</t>
+          <t>Il sent le foin. Sur tes mains aussi. Le poil du poney sent encore le foin.</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -1927,14 +2003,14 @@
       </c>
       <c r="Z6" s="2" t="inlineStr">
         <is>
-          <t>slow</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="AA6" s="2" t="n">
         <v>0.88</v>
       </c>
       <c r="AB6" s="2" t="n">
-        <v>1.26</v>
+        <v>1.22</v>
       </c>
       <c r="AC6" s="2" t="inlineStr">
         <is>
@@ -2006,10 +2082,11 @@
       <c r="AV6" s="2" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
-        </is>
-      </c>
-      <c r="AX6" t="inlineStr"/>
+          <t>enfant-m|Il sent le foin.
+papa|Sur tes mains aussi.
+narrateur|Le poil du poney sent encore le foin.</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV6"/>
@@ -2028,7 +2105,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A5"/>
+  <dimension ref="A1:A6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -2066,6 +2143,13 @@
       <c r="A5" t="inlineStr">
         <is>
           <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>F-NAR-008 récit, pas une leçon en puces</t>
         </is>
       </c>
     </row>

--- a/stories/arbres/ATOM-VIV.ANI.002-08.xlsx
+++ b/stories/arbres/ATOM-VIV.ANI.002-08.xlsx
@@ -671,7 +671,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>écurie et grange</t>
+          <t>écurie, box, paille</t>
         </is>
       </c>
     </row>
@@ -683,7 +683,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Eva, maman, papa</t>
+          <t>Aniss, maman, papa</t>
         </is>
       </c>
     </row>
